--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -24,6 +24,49 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>LDYQ</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>LDYQ:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 衣服
+1 武器
+2 勋章
+3 项链
+4 头盔
+5  右手镯
+6  左手镯
+7  右戒指
+8  左戒指
+9  符、毒药
+10 腰带
+11 鞋子</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6887,7 +6930,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -7197,6 +7240,17 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -82854,5 +82908,6 @@
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -16379,7 +16379,7 @@
         <v>263</v>
       </c>
       <c r="E75" s="14">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F75" s="14">
         <v>0</v>
@@ -16454,7 +16454,7 @@
         <v>267</v>
       </c>
       <c r="E76" s="14">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F76" s="14">
         <v>121</v>
@@ -16527,7 +16527,7 @@
         <v>268</v>
       </c>
       <c r="E77" s="14">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F77" s="14">
         <v>120</v>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="22110" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="EquipProto" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3524" uniqueCount="2269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="2270">
   <si>
     <t>Id</t>
   </si>
@@ -6921,6 +6921,9 @@
   </si>
   <si>
     <t>测试布衣(女)</t>
+  </si>
+  <si>
+    <t>测试项链</t>
   </si>
 </sst>
 </file>
@@ -31971,7 +31974,7 @@
         <v>709</v>
       </c>
       <c r="E287" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F287" s="14">
         <v>29</v>
@@ -32046,7 +32049,7 @@
         <v>711</v>
       </c>
       <c r="E288" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F288" s="14">
         <v>29</v>
@@ -32121,7 +32124,7 @@
         <v>713</v>
       </c>
       <c r="E289" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F289" s="14">
         <v>29</v>
@@ -32196,7 +32199,7 @@
         <v>716</v>
       </c>
       <c r="E290" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F290" s="14">
         <v>29</v>
@@ -32271,7 +32274,7 @@
         <v>718</v>
       </c>
       <c r="E291" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F291" s="14">
         <v>29</v>
@@ -32346,7 +32349,7 @@
         <v>720</v>
       </c>
       <c r="E292" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F292" s="14">
         <v>29</v>
@@ -32421,7 +32424,7 @@
         <v>722</v>
       </c>
       <c r="E293" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F293" s="14">
         <v>29</v>
@@ -32496,7 +32499,7 @@
         <v>725</v>
       </c>
       <c r="E294" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F294" s="14">
         <v>29</v>
@@ -32571,7 +32574,7 @@
         <v>727</v>
       </c>
       <c r="E295" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F295" s="14">
         <v>3</v>
@@ -32721,7 +32724,7 @@
         <v>731</v>
       </c>
       <c r="E297" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F297" s="14">
         <v>4</v>
@@ -32796,7 +32799,7 @@
         <v>734</v>
       </c>
       <c r="E298" s="14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F298" s="14">
         <v>4</v>
@@ -81764,7 +81767,7 @@
         <v>2262</v>
       </c>
       <c r="E914" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F914" s="3">
         <v>30927</v>
@@ -81847,7 +81850,7 @@
         <v>2264</v>
       </c>
       <c r="E915" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F915" s="3">
         <v>30927</v>
@@ -81930,7 +81933,7 @@
         <v>2266</v>
       </c>
       <c r="E916" s="14">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F916" s="14">
         <v>1</v>
@@ -82005,7 +82008,7 @@
         <v>2268</v>
       </c>
       <c r="E917" s="14">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F917" s="14">
         <v>1</v>
@@ -82072,44 +82075,80 @@
       <c r="AL917" s="3"/>
       <c r="AM917" s="3"/>
     </row>
-    <row r="918" customHeight="1" spans="3:39">
-      <c r="C918" s="48"/>
-      <c r="D918" s="48"/>
-      <c r="E918" s="48"/>
-      <c r="F918" s="48"/>
-      <c r="G918" s="48"/>
-      <c r="H918" s="48"/>
-      <c r="I918" s="48"/>
-      <c r="J918" s="48"/>
-      <c r="K918" s="48"/>
-      <c r="L918" s="48"/>
-      <c r="M918" s="48"/>
-      <c r="N918" s="48"/>
-      <c r="O918" s="48"/>
-      <c r="P918" s="48"/>
-      <c r="Q918" s="48"/>
-      <c r="R918" s="48"/>
-      <c r="S918" s="48"/>
-      <c r="T918" s="48"/>
-      <c r="U918" s="48"/>
-      <c r="V918" s="48"/>
-      <c r="W918" s="48"/>
-      <c r="X918" s="49"/>
-      <c r="Y918" s="48"/>
-      <c r="Z918" s="48"/>
-      <c r="AA918" s="50"/>
-      <c r="AB918" s="48"/>
-      <c r="AC918" s="48"/>
-      <c r="AD918" s="48"/>
-      <c r="AE918" s="48"/>
-      <c r="AF918" s="48"/>
-      <c r="AG918" s="48"/>
-      <c r="AH918" s="48"/>
-      <c r="AI918" s="48"/>
-      <c r="AJ918" s="48"/>
-      <c r="AK918" s="48"/>
-      <c r="AL918" s="48"/>
-      <c r="AM918" s="48"/>
+    <row r="918" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C918" s="18">
+        <v>50913</v>
+      </c>
+      <c r="D918" s="15" t="s">
+        <v>2269</v>
+      </c>
+      <c r="E918" s="14">
+        <v>3</v>
+      </c>
+      <c r="F918" s="14">
+        <v>0</v>
+      </c>
+      <c r="G918" s="14">
+        <v>1</v>
+      </c>
+      <c r="H918" s="14">
+        <v>0</v>
+      </c>
+      <c r="I918" s="14">
+        <v>0</v>
+      </c>
+      <c r="J918" s="14">
+        <v>0</v>
+      </c>
+      <c r="K918" s="14">
+        <v>218</v>
+      </c>
+      <c r="L918" s="14">
+        <v>10000</v>
+      </c>
+      <c r="M918" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="N918" s="14">
+        <v>0</v>
+      </c>
+      <c r="O918" s="14">
+        <v>0</v>
+      </c>
+      <c r="P918" s="14">
+        <v>1</v>
+      </c>
+      <c r="Q918" s="14">
+        <v>255</v>
+      </c>
+      <c r="R918" s="14"/>
+      <c r="S918" s="14"/>
+      <c r="T918" s="14"/>
+      <c r="U918" s="14">
+        <v>100</v>
+      </c>
+      <c r="V918" s="14"/>
+      <c r="W918" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="X918" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="Y918" s="14"/>
+      <c r="Z918" s="14"/>
+      <c r="AA918" s="14"/>
+      <c r="AB918" s="14"/>
+      <c r="AC918" s="14"/>
+      <c r="AD918" s="14"/>
+      <c r="AE918" s="14"/>
+      <c r="AF918" s="14"/>
+      <c r="AG918" s="14"/>
+      <c r="AH918" s="3"/>
+      <c r="AI918" s="14"/>
+      <c r="AJ918" s="3"/>
+      <c r="AK918" s="3"/>
+      <c r="AL918" s="3"/>
+      <c r="AM918" s="3"/>
     </row>
     <row r="919" customHeight="1" spans="3:39">
       <c r="C919" s="48"/>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3528" uniqueCount="2270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3533" uniqueCount="2273">
   <si>
     <t>Id</t>
   </si>
@@ -6905,6 +6905,9 @@
     <t>测试武器</t>
   </si>
   <si>
+    <t>000095</t>
+  </si>
+  <si>
     <t>3#3#500|3#4#500|3#5#500|3#6#500|3#7#500|3#8#500|3#13#5|3#14#3|3#39#9|3#20#2</t>
   </si>
   <si>
@@ -6917,6 +6920,9 @@
     <t>测试布衣(男)</t>
   </si>
   <si>
+    <t>000564</t>
+  </si>
+  <si>
     <t>3#9#500|3#10#500|3#11#500|3#12#500</t>
   </si>
   <si>
@@ -6924,6 +6930,9 @@
   </si>
   <si>
     <t>测试项链</t>
+  </si>
+  <si>
+    <t>000127</t>
   </si>
 </sst>
 </file>
@@ -9152,6 +9161,9 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="474">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -11074,7 +11086,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L5" s="12" t="s">
         <v>66</v>
@@ -81534,10 +81546,10 @@
       <c r="I911" s="18">
         <v>0</v>
       </c>
-      <c r="J911" s="18">
-        <v>0</v>
-      </c>
-      <c r="K911" s="18">
+      <c r="J911" s="3">
+        <v>0</v>
+      </c>
+      <c r="K911" s="3">
         <v>12803</v>
       </c>
       <c r="L911" s="18">
@@ -81615,10 +81627,10 @@
       <c r="I912" s="18">
         <v>0</v>
       </c>
-      <c r="J912" s="18">
-        <v>0</v>
-      </c>
-      <c r="K912" s="18">
+      <c r="J912" s="3">
+        <v>0</v>
+      </c>
+      <c r="K912" s="3">
         <v>12804</v>
       </c>
       <c r="L912" s="15">
@@ -81698,10 +81710,10 @@
       <c r="I913" s="18">
         <v>0</v>
       </c>
-      <c r="J913" s="18">
-        <v>0</v>
-      </c>
-      <c r="K913" s="18">
+      <c r="J913" s="3">
+        <v>0</v>
+      </c>
+      <c r="K913" s="3">
         <v>12804</v>
       </c>
       <c r="L913" s="15">
@@ -81784,14 +81796,14 @@
       <c r="J914" s="3">
         <v>0</v>
       </c>
-      <c r="K914" s="3">
-        <v>12733</v>
+      <c r="K914" s="51" t="s">
+        <v>2263</v>
       </c>
       <c r="L914" s="3">
         <v>100000</v>
       </c>
       <c r="M914" s="48" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="N914" s="3">
         <v>0</v>
@@ -81847,7 +81859,7 @@
         <v>50910</v>
       </c>
       <c r="D915" s="3" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="E915" s="3">
         <v>1</v>
@@ -81867,14 +81879,14 @@
       <c r="J915" s="3">
         <v>0</v>
       </c>
-      <c r="K915" s="3">
-        <v>12733</v>
+      <c r="K915" s="51" t="s">
+        <v>2263</v>
       </c>
       <c r="L915" s="3">
         <v>100000</v>
       </c>
       <c r="M915" s="48" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="N915" s="3">
         <v>0</v>
@@ -81930,7 +81942,7 @@
         <v>50911</v>
       </c>
       <c r="D916" s="15" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="E916" s="14">
         <v>0</v>
@@ -81947,17 +81959,17 @@
       <c r="I916" s="14">
         <v>0</v>
       </c>
-      <c r="J916" s="14">
-        <v>0</v>
-      </c>
-      <c r="K916" s="14">
-        <v>60</v>
+      <c r="J916" s="3">
+        <v>0</v>
+      </c>
+      <c r="K916" s="51" t="s">
+        <v>2268</v>
       </c>
       <c r="L916" s="14">
         <v>5000</v>
       </c>
       <c r="M916" s="15" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="N916" s="14">
         <v>0</v>
@@ -82005,34 +82017,34 @@
         <v>50912</v>
       </c>
       <c r="D917" s="15" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E917" s="14">
+        <v>0</v>
+      </c>
+      <c r="F917" s="14">
+        <v>1</v>
+      </c>
+      <c r="G917" s="14">
+        <v>0</v>
+      </c>
+      <c r="H917" s="14">
+        <v>0</v>
+      </c>
+      <c r="I917" s="14">
+        <v>0</v>
+      </c>
+      <c r="J917" s="3">
+        <v>0</v>
+      </c>
+      <c r="K917" s="51" t="s">
         <v>2268</v>
-      </c>
-      <c r="E917" s="14">
-        <v>0</v>
-      </c>
-      <c r="F917" s="14">
-        <v>1</v>
-      </c>
-      <c r="G917" s="14">
-        <v>0</v>
-      </c>
-      <c r="H917" s="14">
-        <v>0</v>
-      </c>
-      <c r="I917" s="14">
-        <v>0</v>
-      </c>
-      <c r="J917" s="14">
-        <v>0</v>
-      </c>
-      <c r="K917" s="14">
-        <v>60</v>
       </c>
       <c r="L917" s="14">
         <v>5000</v>
       </c>
       <c r="M917" s="15" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="N917" s="14">
         <v>0</v>
@@ -82080,7 +82092,7 @@
         <v>50913</v>
       </c>
       <c r="D918" s="15" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="E918" s="14">
         <v>3</v>
@@ -82097,11 +82109,11 @@
       <c r="I918" s="14">
         <v>0</v>
       </c>
-      <c r="J918" s="14">
-        <v>0</v>
-      </c>
-      <c r="K918" s="14">
-        <v>218</v>
+      <c r="J918" s="3">
+        <v>0</v>
+      </c>
+      <c r="K918" s="51" t="s">
+        <v>2272</v>
       </c>
       <c r="L918" s="14">
         <v>10000</v>
@@ -82158,8 +82170,8 @@
       <c r="G919" s="48"/>
       <c r="H919" s="48"/>
       <c r="I919" s="48"/>
-      <c r="J919" s="48"/>
-      <c r="K919" s="48"/>
+      <c r="J919" s="3"/>
+      <c r="K919" s="3"/>
       <c r="L919" s="48"/>
       <c r="M919" s="48"/>
       <c r="N919" s="48"/>
@@ -82197,8 +82209,8 @@
       <c r="G920" s="48"/>
       <c r="H920" s="48"/>
       <c r="I920" s="48"/>
-      <c r="J920" s="48"/>
-      <c r="K920" s="48"/>
+      <c r="J920" s="3"/>
+      <c r="K920" s="3"/>
       <c r="L920" s="48"/>
       <c r="M920" s="48"/>
       <c r="N920" s="48"/>
@@ -82236,8 +82248,8 @@
       <c r="G921" s="48"/>
       <c r="H921" s="48"/>
       <c r="I921" s="48"/>
-      <c r="J921" s="48"/>
-      <c r="K921" s="48"/>
+      <c r="J921" s="3"/>
+      <c r="K921" s="3"/>
       <c r="L921" s="48"/>
       <c r="M921" s="48"/>
       <c r="N921" s="48"/>
@@ -82275,8 +82287,8 @@
       <c r="G922" s="48"/>
       <c r="H922" s="48"/>
       <c r="I922" s="48"/>
-      <c r="J922" s="48"/>
-      <c r="K922" s="48"/>
+      <c r="J922" s="3"/>
+      <c r="K922" s="3"/>
       <c r="L922" s="48"/>
       <c r="M922" s="48"/>
       <c r="N922" s="48"/>
@@ -82314,8 +82326,8 @@
       <c r="G923" s="48"/>
       <c r="H923" s="48"/>
       <c r="I923" s="48"/>
-      <c r="J923" s="48"/>
-      <c r="K923" s="48"/>
+      <c r="J923" s="3"/>
+      <c r="K923" s="3"/>
       <c r="L923" s="48"/>
       <c r="M923" s="48"/>
       <c r="N923" s="48"/>
@@ -82353,8 +82365,8 @@
       <c r="G924" s="48"/>
       <c r="H924" s="48"/>
       <c r="I924" s="48"/>
-      <c r="J924" s="48"/>
-      <c r="K924" s="48"/>
+      <c r="J924" s="3"/>
+      <c r="K924" s="3"/>
       <c r="L924" s="48"/>
       <c r="M924" s="48"/>
       <c r="N924" s="48"/>
@@ -82392,8 +82404,8 @@
       <c r="G925" s="48"/>
       <c r="H925" s="48"/>
       <c r="I925" s="48"/>
-      <c r="J925" s="48"/>
-      <c r="K925" s="48"/>
+      <c r="J925" s="3"/>
+      <c r="K925" s="3"/>
       <c r="L925" s="48"/>
       <c r="M925" s="48"/>
       <c r="N925" s="48"/>
@@ -82431,8 +82443,8 @@
       <c r="G926" s="48"/>
       <c r="H926" s="48"/>
       <c r="I926" s="48"/>
-      <c r="J926" s="48"/>
-      <c r="K926" s="48"/>
+      <c r="J926" s="3"/>
+      <c r="K926" s="3"/>
       <c r="L926" s="48"/>
       <c r="M926" s="48"/>
       <c r="N926" s="48"/>
@@ -82470,8 +82482,8 @@
       <c r="G927" s="48"/>
       <c r="H927" s="48"/>
       <c r="I927" s="48"/>
-      <c r="J927" s="48"/>
-      <c r="K927" s="48"/>
+      <c r="J927" s="3"/>
+      <c r="K927" s="3"/>
       <c r="L927" s="48"/>
       <c r="M927" s="48"/>
       <c r="N927" s="48"/>
@@ -82509,8 +82521,8 @@
       <c r="G928" s="48"/>
       <c r="H928" s="48"/>
       <c r="I928" s="48"/>
-      <c r="J928" s="48"/>
-      <c r="K928" s="48"/>
+      <c r="J928" s="3"/>
+      <c r="K928" s="3"/>
       <c r="L928" s="48"/>
       <c r="M928" s="48"/>
       <c r="N928" s="48"/>
@@ -82548,8 +82560,8 @@
       <c r="G929" s="48"/>
       <c r="H929" s="48"/>
       <c r="I929" s="48"/>
-      <c r="J929" s="48"/>
-      <c r="K929" s="48"/>
+      <c r="J929" s="3"/>
+      <c r="K929" s="3"/>
       <c r="L929" s="48"/>
       <c r="M929" s="48"/>
       <c r="N929" s="48"/>

--- a/Unity/Assets/Config/Excel/EquipConfig.xlsx
+++ b/Unity/Assets/Config/Excel/EquipConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22110" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="EquipProto" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3533" uniqueCount="2273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3575" uniqueCount="2291">
   <si>
     <t>Id</t>
   </si>
@@ -6933,6 +6933,60 @@
   </si>
   <si>
     <t>000127</t>
+  </si>
+  <si>
+    <t>测试精灵头盔</t>
+  </si>
+  <si>
+    <t>000115</t>
+  </si>
+  <si>
+    <t>测试荣誉勋章11号</t>
+  </si>
+  <si>
+    <t>000135</t>
+  </si>
+  <si>
+    <t>测试铁手镯右边</t>
+  </si>
+  <si>
+    <t>000119</t>
+  </si>
+  <si>
+    <t>测试铁手镯左边</t>
+  </si>
+  <si>
+    <t>000505</t>
+  </si>
+  <si>
+    <t>测试护身符</t>
+  </si>
+  <si>
+    <t>000614</t>
+  </si>
+  <si>
+    <t>测试神秘腰带</t>
+  </si>
+  <si>
+    <t>002737</t>
+  </si>
+  <si>
+    <t>测试鹿皮靴</t>
+  </si>
+  <si>
+    <t>000132</t>
+  </si>
+  <si>
+    <t>测试龙之戒指右边</t>
+  </si>
+  <si>
+    <t>000034</t>
+  </si>
+  <si>
+    <t>测试龙之戒指左边</t>
+  </si>
+  <si>
+    <t>000032</t>
   </si>
 </sst>
 </file>
@@ -9164,6 +9218,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" quotePrefix="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="474">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -82162,356 +82219,674 @@
       <c r="AL918" s="3"/>
       <c r="AM918" s="3"/>
     </row>
-    <row r="919" customHeight="1" spans="3:39">
-      <c r="C919" s="48"/>
-      <c r="D919" s="48"/>
-      <c r="E919" s="48"/>
-      <c r="F919" s="48"/>
-      <c r="G919" s="48"/>
-      <c r="H919" s="48"/>
-      <c r="I919" s="48"/>
-      <c r="J919" s="3"/>
-      <c r="K919" s="3"/>
-      <c r="L919" s="48"/>
-      <c r="M919" s="48"/>
-      <c r="N919" s="48"/>
-      <c r="O919" s="48"/>
-      <c r="P919" s="48"/>
-      <c r="Q919" s="48"/>
-      <c r="R919" s="48"/>
-      <c r="S919" s="48"/>
-      <c r="T919" s="48"/>
-      <c r="U919" s="48"/>
-      <c r="V919" s="48"/>
-      <c r="W919" s="48"/>
-      <c r="X919" s="49"/>
-      <c r="Y919" s="48"/>
-      <c r="Z919" s="48"/>
-      <c r="AA919" s="50"/>
-      <c r="AB919" s="48"/>
-      <c r="AC919" s="48"/>
-      <c r="AD919" s="48"/>
-      <c r="AE919" s="48"/>
-      <c r="AF919" s="48"/>
-      <c r="AG919" s="48"/>
-      <c r="AH919" s="48"/>
-      <c r="AI919" s="48"/>
-      <c r="AJ919" s="48"/>
-      <c r="AK919" s="48"/>
-      <c r="AL919" s="48"/>
-      <c r="AM919" s="48"/>
-    </row>
-    <row r="920" customHeight="1" spans="3:39">
-      <c r="C920" s="48"/>
-      <c r="D920" s="48"/>
-      <c r="E920" s="48"/>
-      <c r="F920" s="48"/>
-      <c r="G920" s="48"/>
-      <c r="H920" s="48"/>
-      <c r="I920" s="48"/>
-      <c r="J920" s="3"/>
-      <c r="K920" s="3"/>
-      <c r="L920" s="48"/>
-      <c r="M920" s="48"/>
-      <c r="N920" s="48"/>
-      <c r="O920" s="48"/>
-      <c r="P920" s="48"/>
-      <c r="Q920" s="48"/>
-      <c r="R920" s="48"/>
-      <c r="S920" s="48"/>
-      <c r="T920" s="48"/>
-      <c r="U920" s="48"/>
-      <c r="V920" s="48"/>
-      <c r="W920" s="48"/>
-      <c r="X920" s="49"/>
-      <c r="Y920" s="48"/>
-      <c r="Z920" s="48"/>
-      <c r="AA920" s="50"/>
-      <c r="AB920" s="48"/>
-      <c r="AC920" s="48"/>
-      <c r="AD920" s="48"/>
-      <c r="AE920" s="48"/>
-      <c r="AF920" s="48"/>
-      <c r="AG920" s="48"/>
-      <c r="AH920" s="48"/>
-      <c r="AI920" s="48"/>
-      <c r="AJ920" s="48"/>
-      <c r="AK920" s="48"/>
-      <c r="AL920" s="48"/>
-      <c r="AM920" s="48"/>
-    </row>
-    <row r="921" customHeight="1" spans="3:39">
-      <c r="C921" s="48"/>
-      <c r="D921" s="48"/>
-      <c r="E921" s="48"/>
-      <c r="F921" s="48"/>
-      <c r="G921" s="48"/>
-      <c r="H921" s="48"/>
-      <c r="I921" s="48"/>
-      <c r="J921" s="3"/>
-      <c r="K921" s="3"/>
-      <c r="L921" s="48"/>
-      <c r="M921" s="48"/>
-      <c r="N921" s="48"/>
-      <c r="O921" s="48"/>
-      <c r="P921" s="48"/>
-      <c r="Q921" s="48"/>
-      <c r="R921" s="48"/>
-      <c r="S921" s="48"/>
-      <c r="T921" s="48"/>
-      <c r="U921" s="48"/>
-      <c r="V921" s="48"/>
-      <c r="W921" s="48"/>
-      <c r="X921" s="49"/>
-      <c r="Y921" s="48"/>
-      <c r="Z921" s="48"/>
-      <c r="AA921" s="50"/>
-      <c r="AB921" s="48"/>
-      <c r="AC921" s="48"/>
-      <c r="AD921" s="48"/>
-      <c r="AE921" s="48"/>
-      <c r="AF921" s="48"/>
-      <c r="AG921" s="48"/>
-      <c r="AH921" s="48"/>
-      <c r="AI921" s="48"/>
-      <c r="AJ921" s="48"/>
-      <c r="AK921" s="48"/>
-      <c r="AL921" s="48"/>
-      <c r="AM921" s="48"/>
-    </row>
-    <row r="922" customHeight="1" spans="3:39">
-      <c r="C922" s="48"/>
-      <c r="D922" s="48"/>
-      <c r="E922" s="48"/>
-      <c r="F922" s="48"/>
-      <c r="G922" s="48"/>
-      <c r="H922" s="48"/>
-      <c r="I922" s="48"/>
-      <c r="J922" s="3"/>
-      <c r="K922" s="3"/>
-      <c r="L922" s="48"/>
-      <c r="M922" s="48"/>
-      <c r="N922" s="48"/>
-      <c r="O922" s="48"/>
-      <c r="P922" s="48"/>
-      <c r="Q922" s="48"/>
-      <c r="R922" s="48"/>
-      <c r="S922" s="48"/>
-      <c r="T922" s="48"/>
-      <c r="U922" s="48"/>
-      <c r="V922" s="48"/>
-      <c r="W922" s="48"/>
-      <c r="X922" s="49"/>
-      <c r="Y922" s="48"/>
-      <c r="Z922" s="48"/>
-      <c r="AA922" s="50"/>
-      <c r="AB922" s="48"/>
-      <c r="AC922" s="48"/>
-      <c r="AD922" s="48"/>
-      <c r="AE922" s="48"/>
-      <c r="AF922" s="48"/>
-      <c r="AG922" s="48"/>
-      <c r="AH922" s="48"/>
-      <c r="AI922" s="48"/>
-      <c r="AJ922" s="48"/>
-      <c r="AK922" s="48"/>
-      <c r="AL922" s="48"/>
-      <c r="AM922" s="48"/>
-    </row>
-    <row r="923" customHeight="1" spans="3:39">
-      <c r="C923" s="48"/>
-      <c r="D923" s="48"/>
-      <c r="E923" s="48"/>
-      <c r="F923" s="48"/>
-      <c r="G923" s="48"/>
-      <c r="H923" s="48"/>
-      <c r="I923" s="48"/>
-      <c r="J923" s="3"/>
-      <c r="K923" s="3"/>
-      <c r="L923" s="48"/>
-      <c r="M923" s="48"/>
-      <c r="N923" s="48"/>
-      <c r="O923" s="48"/>
-      <c r="P923" s="48"/>
-      <c r="Q923" s="48"/>
-      <c r="R923" s="48"/>
-      <c r="S923" s="48"/>
-      <c r="T923" s="48"/>
-      <c r="U923" s="48"/>
-      <c r="V923" s="48"/>
-      <c r="W923" s="48"/>
-      <c r="X923" s="49"/>
-      <c r="Y923" s="48"/>
-      <c r="Z923" s="48"/>
-      <c r="AA923" s="50"/>
-      <c r="AB923" s="48"/>
-      <c r="AC923" s="48"/>
-      <c r="AD923" s="48"/>
-      <c r="AE923" s="48"/>
-      <c r="AF923" s="48"/>
-      <c r="AG923" s="48"/>
-      <c r="AH923" s="48"/>
-      <c r="AI923" s="48"/>
-      <c r="AJ923" s="48"/>
-      <c r="AK923" s="48"/>
-      <c r="AL923" s="48"/>
-      <c r="AM923" s="48"/>
-    </row>
-    <row r="924" customHeight="1" spans="3:39">
-      <c r="C924" s="48"/>
-      <c r="D924" s="48"/>
-      <c r="E924" s="48"/>
-      <c r="F924" s="48"/>
-      <c r="G924" s="48"/>
-      <c r="H924" s="48"/>
-      <c r="I924" s="48"/>
-      <c r="J924" s="3"/>
-      <c r="K924" s="3"/>
-      <c r="L924" s="48"/>
-      <c r="M924" s="48"/>
-      <c r="N924" s="48"/>
-      <c r="O924" s="48"/>
-      <c r="P924" s="48"/>
-      <c r="Q924" s="48"/>
-      <c r="R924" s="48"/>
-      <c r="S924" s="48"/>
-      <c r="T924" s="48"/>
-      <c r="U924" s="48"/>
-      <c r="V924" s="48"/>
-      <c r="W924" s="48"/>
-      <c r="X924" s="49"/>
-      <c r="Y924" s="48"/>
-      <c r="Z924" s="48"/>
-      <c r="AA924" s="50"/>
-      <c r="AB924" s="48"/>
-      <c r="AC924" s="48"/>
-      <c r="AD924" s="48"/>
-      <c r="AE924" s="48"/>
-      <c r="AF924" s="48"/>
-      <c r="AG924" s="48"/>
-      <c r="AH924" s="48"/>
-      <c r="AI924" s="48"/>
-      <c r="AJ924" s="48"/>
-      <c r="AK924" s="48"/>
-      <c r="AL924" s="48"/>
-      <c r="AM924" s="48"/>
-    </row>
-    <row r="925" customHeight="1" spans="3:39">
-      <c r="C925" s="48"/>
-      <c r="D925" s="48"/>
-      <c r="E925" s="48"/>
-      <c r="F925" s="48"/>
-      <c r="G925" s="48"/>
-      <c r="H925" s="48"/>
-      <c r="I925" s="48"/>
-      <c r="J925" s="3"/>
-      <c r="K925" s="3"/>
-      <c r="L925" s="48"/>
-      <c r="M925" s="48"/>
-      <c r="N925" s="48"/>
-      <c r="O925" s="48"/>
-      <c r="P925" s="48"/>
-      <c r="Q925" s="48"/>
-      <c r="R925" s="48"/>
-      <c r="S925" s="48"/>
-      <c r="T925" s="48"/>
-      <c r="U925" s="48"/>
-      <c r="V925" s="48"/>
-      <c r="W925" s="48"/>
-      <c r="X925" s="49"/>
-      <c r="Y925" s="48"/>
-      <c r="Z925" s="48"/>
-      <c r="AA925" s="50"/>
-      <c r="AB925" s="48"/>
-      <c r="AC925" s="48"/>
-      <c r="AD925" s="48"/>
-      <c r="AE925" s="48"/>
-      <c r="AF925" s="48"/>
-      <c r="AG925" s="48"/>
-      <c r="AH925" s="48"/>
-      <c r="AI925" s="48"/>
-      <c r="AJ925" s="48"/>
-      <c r="AK925" s="48"/>
-      <c r="AL925" s="48"/>
-      <c r="AM925" s="48"/>
-    </row>
-    <row r="926" customHeight="1" spans="3:39">
-      <c r="C926" s="48"/>
-      <c r="D926" s="48"/>
-      <c r="E926" s="48"/>
-      <c r="F926" s="48"/>
-      <c r="G926" s="48"/>
-      <c r="H926" s="48"/>
-      <c r="I926" s="48"/>
-      <c r="J926" s="3"/>
-      <c r="K926" s="3"/>
-      <c r="L926" s="48"/>
-      <c r="M926" s="48"/>
-      <c r="N926" s="48"/>
-      <c r="O926" s="48"/>
-      <c r="P926" s="48"/>
-      <c r="Q926" s="48"/>
-      <c r="R926" s="48"/>
-      <c r="S926" s="48"/>
-      <c r="T926" s="48"/>
-      <c r="U926" s="48"/>
-      <c r="V926" s="48"/>
-      <c r="W926" s="48"/>
-      <c r="X926" s="49"/>
-      <c r="Y926" s="48"/>
-      <c r="Z926" s="48"/>
-      <c r="AA926" s="50"/>
-      <c r="AB926" s="48"/>
-      <c r="AC926" s="48"/>
-      <c r="AD926" s="48"/>
-      <c r="AE926" s="48"/>
-      <c r="AF926" s="48"/>
-      <c r="AG926" s="48"/>
-      <c r="AH926" s="48"/>
-      <c r="AI926" s="48"/>
-      <c r="AJ926" s="48"/>
-      <c r="AK926" s="48"/>
-      <c r="AL926" s="48"/>
-      <c r="AM926" s="48"/>
-    </row>
-    <row r="927" customHeight="1" spans="3:39">
-      <c r="C927" s="48"/>
-      <c r="D927" s="48"/>
-      <c r="E927" s="48"/>
-      <c r="F927" s="48"/>
-      <c r="G927" s="48"/>
-      <c r="H927" s="48"/>
-      <c r="I927" s="48"/>
-      <c r="J927" s="3"/>
-      <c r="K927" s="3"/>
-      <c r="L927" s="48"/>
-      <c r="M927" s="48"/>
-      <c r="N927" s="48"/>
-      <c r="O927" s="48"/>
-      <c r="P927" s="48"/>
-      <c r="Q927" s="48"/>
-      <c r="R927" s="48"/>
-      <c r="S927" s="48"/>
-      <c r="T927" s="48"/>
-      <c r="U927" s="48"/>
-      <c r="V927" s="48"/>
-      <c r="W927" s="48"/>
-      <c r="X927" s="49"/>
-      <c r="Y927" s="48"/>
-      <c r="Z927" s="48"/>
-      <c r="AA927" s="50"/>
-      <c r="AB927" s="48"/>
-      <c r="AC927" s="48"/>
-      <c r="AD927" s="48"/>
-      <c r="AE927" s="48"/>
-      <c r="AF927" s="48"/>
-      <c r="AG927" s="48"/>
-      <c r="AH927" s="48"/>
-      <c r="AI927" s="48"/>
-      <c r="AJ927" s="48"/>
-      <c r="AK927" s="48"/>
-      <c r="AL927" s="48"/>
-      <c r="AM927" s="48"/>
+    <row r="919" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C919" s="18">
+        <v>50914</v>
+      </c>
+      <c r="D919" s="15" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E919" s="14">
+        <v>4</v>
+      </c>
+      <c r="F919" s="14">
+        <v>0</v>
+      </c>
+      <c r="G919" s="14">
+        <v>5</v>
+      </c>
+      <c r="H919" s="14">
+        <v>0</v>
+      </c>
+      <c r="I919" s="14">
+        <v>0</v>
+      </c>
+      <c r="J919" s="14">
+        <v>0</v>
+      </c>
+      <c r="K919" s="52" t="s">
+        <v>2274</v>
+      </c>
+      <c r="L919" s="14">
+        <v>1000</v>
+      </c>
+      <c r="M919" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="N919" s="14">
+        <v>0</v>
+      </c>
+      <c r="O919" s="14">
+        <v>1</v>
+      </c>
+      <c r="P919" s="14">
+        <v>1000</v>
+      </c>
+      <c r="Q919" s="14">
+        <v>250</v>
+      </c>
+      <c r="R919" s="14"/>
+      <c r="S919" s="14"/>
+      <c r="T919" s="14"/>
+      <c r="U919" s="14">
+        <v>100</v>
+      </c>
+      <c r="V919" s="14"/>
+      <c r="W919" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="X919" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y919" s="14"/>
+      <c r="Z919" s="14"/>
+      <c r="AA919" s="14"/>
+      <c r="AB919" s="14"/>
+      <c r="AC919" s="14"/>
+      <c r="AD919" s="14"/>
+      <c r="AE919" s="14"/>
+      <c r="AF919" s="14"/>
+      <c r="AG919" s="14"/>
+      <c r="AH919" s="3"/>
+      <c r="AI919" s="14"/>
+      <c r="AJ919" s="3"/>
+      <c r="AK919" s="3"/>
+      <c r="AL919" s="3"/>
+      <c r="AM919" s="3"/>
+    </row>
+    <row r="920" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C920" s="18">
+        <v>50915</v>
+      </c>
+      <c r="D920" s="15" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E920" s="14">
+        <v>2</v>
+      </c>
+      <c r="F920" s="14">
+        <v>0</v>
+      </c>
+      <c r="G920" s="14">
+        <v>0</v>
+      </c>
+      <c r="H920" s="14">
+        <v>0</v>
+      </c>
+      <c r="I920" s="14">
+        <v>0</v>
+      </c>
+      <c r="J920" s="14">
+        <v>0</v>
+      </c>
+      <c r="K920" s="52" t="s">
+        <v>2276</v>
+      </c>
+      <c r="L920" s="14">
+        <v>45000</v>
+      </c>
+      <c r="M920" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="N920" s="14">
+        <v>0</v>
+      </c>
+      <c r="O920" s="14">
+        <v>7</v>
+      </c>
+      <c r="P920" s="14">
+        <v>5000</v>
+      </c>
+      <c r="Q920" s="14">
+        <v>255</v>
+      </c>
+      <c r="R920" s="14"/>
+      <c r="S920" s="14"/>
+      <c r="T920" s="14"/>
+      <c r="U920" s="14">
+        <v>100</v>
+      </c>
+      <c r="V920" s="14"/>
+      <c r="W920" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="X920" s="14"/>
+      <c r="Y920" s="14"/>
+      <c r="Z920" s="14"/>
+      <c r="AA920" s="14"/>
+      <c r="AB920" s="14"/>
+      <c r="AC920" s="14"/>
+      <c r="AD920" s="14"/>
+      <c r="AE920" s="14"/>
+      <c r="AF920" s="14"/>
+      <c r="AG920" s="14"/>
+      <c r="AH920" s="3"/>
+      <c r="AI920" s="14"/>
+      <c r="AJ920" s="3"/>
+      <c r="AK920" s="3"/>
+      <c r="AL920" s="3"/>
+      <c r="AM920" s="3"/>
+    </row>
+    <row r="921" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C921" s="18">
+        <v>50916</v>
+      </c>
+      <c r="D921" s="15" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E921" s="14">
+        <v>5</v>
+      </c>
+      <c r="F921" s="14">
+        <v>0</v>
+      </c>
+      <c r="G921" s="14">
+        <v>1</v>
+      </c>
+      <c r="H921" s="14">
+        <v>0</v>
+      </c>
+      <c r="I921" s="14">
+        <v>0</v>
+      </c>
+      <c r="J921" s="14">
+        <v>0</v>
+      </c>
+      <c r="K921" s="52" t="s">
+        <v>2278</v>
+      </c>
+      <c r="L921" s="14">
+        <v>4000</v>
+      </c>
+      <c r="M921" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="N921" s="14">
+        <v>0</v>
+      </c>
+      <c r="O921" s="14">
+        <v>3</v>
+      </c>
+      <c r="P921" s="14">
+        <v>880</v>
+      </c>
+      <c r="Q921" s="14">
+        <v>255</v>
+      </c>
+      <c r="R921" s="14"/>
+      <c r="S921" s="14"/>
+      <c r="T921" s="14"/>
+      <c r="U921" s="14">
+        <v>100</v>
+      </c>
+      <c r="V921" s="14"/>
+      <c r="W921" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="X921" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y921" s="14"/>
+      <c r="Z921" s="14"/>
+      <c r="AA921" s="14"/>
+      <c r="AB921" s="14"/>
+      <c r="AC921" s="14"/>
+      <c r="AD921" s="14"/>
+      <c r="AE921" s="14"/>
+      <c r="AF921" s="14"/>
+      <c r="AG921" s="14"/>
+      <c r="AH921" s="3"/>
+      <c r="AI921" s="14"/>
+      <c r="AJ921" s="3"/>
+      <c r="AK921" s="3"/>
+      <c r="AL921" s="3"/>
+      <c r="AM921" s="3"/>
+    </row>
+    <row r="922" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C922" s="18">
+        <v>50917</v>
+      </c>
+      <c r="D922" s="15" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E922" s="14">
+        <v>6</v>
+      </c>
+      <c r="F922" s="14">
+        <v>0</v>
+      </c>
+      <c r="G922" s="14">
+        <v>1</v>
+      </c>
+      <c r="H922" s="14">
+        <v>0</v>
+      </c>
+      <c r="I922" s="14">
+        <v>0</v>
+      </c>
+      <c r="J922" s="14">
+        <v>0</v>
+      </c>
+      <c r="K922" s="52" t="s">
+        <v>2280</v>
+      </c>
+      <c r="L922" s="14">
+        <v>4000</v>
+      </c>
+      <c r="M922" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="N922" s="14">
+        <v>0</v>
+      </c>
+      <c r="O922" s="14">
+        <v>3</v>
+      </c>
+      <c r="P922" s="14">
+        <v>880</v>
+      </c>
+      <c r="Q922" s="14">
+        <v>255</v>
+      </c>
+      <c r="R922" s="14"/>
+      <c r="S922" s="14"/>
+      <c r="T922" s="14"/>
+      <c r="U922" s="14">
+        <v>100</v>
+      </c>
+      <c r="V922" s="14"/>
+      <c r="W922" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="X922" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y922" s="14"/>
+      <c r="Z922" s="14"/>
+      <c r="AA922" s="14"/>
+      <c r="AB922" s="14"/>
+      <c r="AC922" s="14"/>
+      <c r="AD922" s="14"/>
+      <c r="AE922" s="14"/>
+      <c r="AF922" s="14"/>
+      <c r="AG922" s="14"/>
+      <c r="AH922" s="3"/>
+      <c r="AI922" s="14"/>
+      <c r="AJ922" s="3"/>
+      <c r="AK922" s="3"/>
+      <c r="AL922" s="3"/>
+      <c r="AM922" s="3"/>
+    </row>
+    <row r="923" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C923" s="18">
+        <v>50918</v>
+      </c>
+      <c r="D923" s="15" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E923" s="14">
+        <v>9</v>
+      </c>
+      <c r="F923" s="14">
+        <v>5</v>
+      </c>
+      <c r="G923" s="14">
+        <v>1</v>
+      </c>
+      <c r="H923" s="14">
+        <v>0</v>
+      </c>
+      <c r="I923" s="14">
+        <v>0</v>
+      </c>
+      <c r="J923" s="14">
+        <v>0</v>
+      </c>
+      <c r="K923" s="52" t="s">
+        <v>2282</v>
+      </c>
+      <c r="L923" s="14">
+        <v>10000</v>
+      </c>
+      <c r="M923" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="N923" s="14">
+        <v>0</v>
+      </c>
+      <c r="O923" s="14">
+        <v>0</v>
+      </c>
+      <c r="P923" s="14">
+        <v>500</v>
+      </c>
+      <c r="Q923" s="14">
+        <v>255</v>
+      </c>
+      <c r="R923" s="14"/>
+      <c r="S923" s="14"/>
+      <c r="T923" s="14"/>
+      <c r="U923" s="14">
+        <v>100</v>
+      </c>
+      <c r="V923" s="14"/>
+      <c r="W923" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="X923" s="14"/>
+      <c r="Y923" s="14"/>
+      <c r="Z923" s="14"/>
+      <c r="AA923" s="14"/>
+      <c r="AB923" s="14"/>
+      <c r="AC923" s="14"/>
+      <c r="AD923" s="14"/>
+      <c r="AE923" s="14"/>
+      <c r="AF923" s="14"/>
+      <c r="AG923" s="14"/>
+      <c r="AH923" s="3"/>
+      <c r="AI923" s="14"/>
+      <c r="AJ923" s="3"/>
+      <c r="AK923" s="3"/>
+      <c r="AL923" s="3"/>
+      <c r="AM923" s="3"/>
+    </row>
+    <row r="924" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C924" s="18">
+        <v>50919</v>
+      </c>
+      <c r="D924" s="15" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E924" s="14">
+        <v>10</v>
+      </c>
+      <c r="F924" s="14">
+        <v>131</v>
+      </c>
+      <c r="G924" s="14">
+        <v>1</v>
+      </c>
+      <c r="H924" s="14">
+        <v>0</v>
+      </c>
+      <c r="I924" s="14">
+        <v>0</v>
+      </c>
+      <c r="J924" s="14">
+        <v>0</v>
+      </c>
+      <c r="K924" s="52" t="s">
+        <v>2284</v>
+      </c>
+      <c r="L924" s="14">
+        <v>8000</v>
+      </c>
+      <c r="M924" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="N924" s="14">
+        <v>0</v>
+      </c>
+      <c r="O924" s="14">
+        <v>18</v>
+      </c>
+      <c r="P924" s="14">
+        <v>27</v>
+      </c>
+      <c r="Q924" s="14">
+        <v>250</v>
+      </c>
+      <c r="R924" s="14"/>
+      <c r="S924" s="14"/>
+      <c r="T924" s="14"/>
+      <c r="U924" s="14">
+        <v>100</v>
+      </c>
+      <c r="V924" s="14"/>
+      <c r="W924" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="X924" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y924" s="14"/>
+      <c r="Z924" s="14"/>
+      <c r="AA924" s="14"/>
+      <c r="AB924" s="14"/>
+      <c r="AC924" s="14"/>
+      <c r="AD924" s="14"/>
+      <c r="AE924" s="14"/>
+      <c r="AF924" s="14"/>
+      <c r="AG924" s="14"/>
+      <c r="AH924" s="3"/>
+      <c r="AI924" s="14"/>
+      <c r="AJ924" s="3"/>
+      <c r="AK924" s="3"/>
+      <c r="AL924" s="3"/>
+      <c r="AM924" s="3"/>
+    </row>
+    <row r="925" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C925" s="18">
+        <v>50920</v>
+      </c>
+      <c r="D925" s="15" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E925" s="14">
+        <v>11</v>
+      </c>
+      <c r="F925" s="14">
+        <v>0</v>
+      </c>
+      <c r="G925" s="14">
+        <v>1</v>
+      </c>
+      <c r="H925" s="14">
+        <v>4</v>
+      </c>
+      <c r="I925" s="14">
+        <v>0</v>
+      </c>
+      <c r="J925" s="14">
+        <v>0</v>
+      </c>
+      <c r="K925" s="52" t="s">
+        <v>2286</v>
+      </c>
+      <c r="L925" s="14">
+        <v>6000</v>
+      </c>
+      <c r="M925" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="N925" s="14">
+        <v>0</v>
+      </c>
+      <c r="O925" s="14">
+        <v>22</v>
+      </c>
+      <c r="P925" s="14">
+        <v>20000</v>
+      </c>
+      <c r="Q925" s="14">
+        <v>255</v>
+      </c>
+      <c r="R925" s="14"/>
+      <c r="S925" s="14"/>
+      <c r="T925" s="14"/>
+      <c r="U925" s="14">
+        <v>100</v>
+      </c>
+      <c r="V925" s="14"/>
+      <c r="W925" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="X925" s="14"/>
+      <c r="Y925" s="14"/>
+      <c r="Z925" s="14"/>
+      <c r="AA925" s="14"/>
+      <c r="AB925" s="14"/>
+      <c r="AC925" s="14"/>
+      <c r="AD925" s="14"/>
+      <c r="AE925" s="14"/>
+      <c r="AF925" s="14"/>
+      <c r="AG925" s="14"/>
+      <c r="AH925" s="3"/>
+      <c r="AI925" s="14"/>
+      <c r="AJ925" s="3"/>
+      <c r="AK925" s="3"/>
+      <c r="AL925" s="3"/>
+      <c r="AM925" s="3"/>
+    </row>
+    <row r="926" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C926" s="18">
+        <v>50921</v>
+      </c>
+      <c r="D926" s="15" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E926" s="14">
+        <v>7</v>
+      </c>
+      <c r="F926" s="14">
+        <v>0</v>
+      </c>
+      <c r="G926" s="14">
+        <v>1</v>
+      </c>
+      <c r="H926" s="14">
+        <v>0</v>
+      </c>
+      <c r="I926" s="14">
+        <v>0</v>
+      </c>
+      <c r="J926" s="14">
+        <v>0</v>
+      </c>
+      <c r="K926" s="52" t="s">
+        <v>2288</v>
+      </c>
+      <c r="L926" s="14">
+        <v>5000</v>
+      </c>
+      <c r="M926" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="N926" s="14">
+        <v>0</v>
+      </c>
+      <c r="O926" s="14">
+        <v>20</v>
+      </c>
+      <c r="P926" s="14">
+        <v>15000</v>
+      </c>
+      <c r="Q926" s="14">
+        <v>250</v>
+      </c>
+      <c r="R926" s="14"/>
+      <c r="S926" s="14"/>
+      <c r="T926" s="14"/>
+      <c r="U926" s="14">
+        <v>100</v>
+      </c>
+      <c r="V926" s="14"/>
+      <c r="W926" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="X926" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y926" s="14"/>
+      <c r="Z926" s="14"/>
+      <c r="AA926" s="14"/>
+      <c r="AB926" s="14"/>
+      <c r="AC926" s="14"/>
+      <c r="AD926" s="14"/>
+      <c r="AE926" s="14"/>
+      <c r="AF926" s="14"/>
+      <c r="AG926" s="14"/>
+      <c r="AH926" s="3"/>
+      <c r="AI926" s="14"/>
+      <c r="AJ926" s="3"/>
+      <c r="AK926" s="3"/>
+      <c r="AL926" s="3"/>
+      <c r="AM926" s="3"/>
+    </row>
+    <row r="927" customFormat="1" customHeight="1" spans="3:39">
+      <c r="C927" s="18">
+        <v>50922</v>
+      </c>
+      <c r="D927" s="15" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E927" s="14">
+        <v>8</v>
+      </c>
+      <c r="F927" s="14">
+        <v>0</v>
+      </c>
+      <c r="G927" s="14">
+        <v>1</v>
+      </c>
+      <c r="H927" s="14">
+        <v>0</v>
+      </c>
+      <c r="I927" s="14">
+        <v>0</v>
+      </c>
+      <c r="J927" s="14">
+        <v>0</v>
+      </c>
+      <c r="K927" s="52" t="s">
+        <v>2290</v>
+      </c>
+      <c r="L927" s="14">
+        <v>5000</v>
+      </c>
+      <c r="M927" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="N927" s="14">
+        <v>0</v>
+      </c>
+      <c r="O927" s="14">
+        <v>20</v>
+      </c>
+      <c r="P927" s="14">
+        <v>15000</v>
+      </c>
+      <c r="Q927" s="14">
+        <v>250</v>
+      </c>
+      <c r="R927" s="14"/>
+      <c r="S927" s="14"/>
+      <c r="T927" s="14"/>
+      <c r="U927" s="14">
+        <v>100</v>
+      </c>
+      <c r="V927" s="14"/>
+      <c r="W927" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="X927" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y927" s="14"/>
+      <c r="Z927" s="14"/>
+      <c r="AA927" s="14"/>
+      <c r="AB927" s="14"/>
+      <c r="AC927" s="14"/>
+      <c r="AD927" s="14"/>
+      <c r="AE927" s="14"/>
+      <c r="AF927" s="14"/>
+      <c r="AG927" s="14"/>
+      <c r="AH927" s="3"/>
+      <c r="AI927" s="14"/>
+      <c r="AJ927" s="3"/>
+      <c r="AK927" s="3"/>
+      <c r="AL927" s="3"/>
+      <c r="AM927" s="3"/>
     </row>
     <row r="928" customHeight="1" spans="3:39">
       <c r="C928" s="48"/>
